--- a/pandas-finance-assignment/data_offline/fred_macro.xlsx
+++ b/pandas-finance-assignment/data_offline/fred_macro.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C947"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,656 +464,7727 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B6" t="n">
-        <v>262.467</v>
+        <v>17533</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B7" t="n">
-        <v>263.181</v>
+        <v>17564</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B8" t="n">
-        <v>264.249</v>
+        <v>17593</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B9" t="n">
-        <v>265.435</v>
+        <v>17624</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44317</v>
-      </c>
-      <c r="B10" t="n">
-        <v>266.262</v>
+        <v>17654</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44348</v>
-      </c>
-      <c r="B11" t="n">
-        <v>267.308</v>
+        <v>17685</v>
       </c>
       <c r="C11" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B12" t="n">
-        <v>268.71</v>
+        <v>17715</v>
       </c>
       <c r="C12" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44409</v>
-      </c>
-      <c r="B13" t="n">
-        <v>270.181</v>
+        <v>17746</v>
       </c>
       <c r="C13" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44440</v>
-      </c>
-      <c r="B14" t="n">
-        <v>271.847</v>
+        <v>17777</v>
       </c>
       <c r="C14" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B15" t="n">
-        <v>273.525</v>
+        <v>17807</v>
       </c>
       <c r="C15" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44501</v>
-      </c>
-      <c r="B16" t="n">
-        <v>275.632</v>
+        <v>17838</v>
       </c>
       <c r="C16" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B17" t="n">
-        <v>277.859</v>
+        <v>17868</v>
       </c>
       <c r="C17" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B18" t="n">
-        <v>280.088</v>
+        <v>17899</v>
       </c>
       <c r="C18" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B19" t="n">
-        <v>282.592</v>
+        <v>17930</v>
       </c>
       <c r="C19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="B20" t="n">
-        <v>285.057</v>
+        <v>17958</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B21" t="n">
-        <v>287.333</v>
+        <v>17989</v>
       </c>
       <c r="C21" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="B22" t="n">
-        <v>289.821</v>
+        <v>18019</v>
       </c>
       <c r="C22" t="n">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B23" t="n">
-        <v>292.05</v>
+        <v>18050</v>
       </c>
       <c r="C23" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B24" t="n">
-        <v>294.535</v>
+        <v>18080</v>
       </c>
       <c r="C24" t="n">
-        <v>4.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="B25" t="n">
-        <v>296.769</v>
+        <v>18111</v>
       </c>
       <c r="C25" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B26" t="n">
-        <v>298.865</v>
+        <v>18142</v>
       </c>
       <c r="C26" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B27" t="n">
-        <v>300.741</v>
+        <v>18172</v>
       </c>
       <c r="C27" t="n">
-        <v>3.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B28" t="n">
-        <v>302.819</v>
+        <v>18203</v>
       </c>
       <c r="C28" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B29" t="n">
-        <v>304.506</v>
+        <v>18233</v>
       </c>
       <c r="C29" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B30" t="n">
-        <v>306.001</v>
+        <v>18264</v>
       </c>
       <c r="C30" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B31" t="n">
-        <v>307.377</v>
+        <v>18295</v>
       </c>
       <c r="C31" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B32" t="n">
-        <v>308.794</v>
+        <v>18323</v>
       </c>
       <c r="C32" t="n">
-        <v>3.7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B33" t="n">
-        <v>310.072</v>
+        <v>18354</v>
       </c>
       <c r="C33" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B34" t="n">
-        <v>311.268</v>
+        <v>18384</v>
       </c>
       <c r="C34" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B35" t="n">
-        <v>312.389</v>
+        <v>18415</v>
       </c>
       <c r="C35" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B36" t="n">
-        <v>313.769</v>
+        <v>18445</v>
       </c>
       <c r="C36" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B37" t="n">
-        <v>314.623</v>
+        <v>18476</v>
       </c>
       <c r="C37" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B38" t="n">
-        <v>315.418</v>
+        <v>18507</v>
       </c>
       <c r="C38" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B39" t="n">
-        <v>316.126</v>
+        <v>18537</v>
       </c>
       <c r="C39" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B40" t="n">
-        <v>317.085</v>
+        <v>18568</v>
       </c>
       <c r="C40" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B41" t="n">
-        <v>318.127</v>
+        <v>18598</v>
       </c>
       <c r="C41" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B42" t="n">
-        <v>318.924</v>
+        <v>18629</v>
       </c>
       <c r="C42" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B43" t="n">
-        <v>319.575</v>
+        <v>18660</v>
       </c>
       <c r="C43" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B44" t="n">
-        <v>320.226</v>
+        <v>18688</v>
       </c>
       <c r="C44" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B45" t="n">
-        <v>321.158</v>
+        <v>18719</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B46" t="n">
-        <v>322.107</v>
+        <v>18749</v>
       </c>
       <c r="C46" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B47" t="n">
-        <v>323.02</v>
+        <v>18780</v>
       </c>
       <c r="C47" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45474</v>
-      </c>
-      <c r="B48" t="n">
-        <v>323.7</v>
+        <v>18810</v>
       </c>
       <c r="C48" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45505</v>
-      </c>
-      <c r="B49" t="n">
-        <v>324.555</v>
+        <v>18841</v>
       </c>
       <c r="C49" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45536</v>
-      </c>
-      <c r="B50" t="n">
-        <v>325.389</v>
+        <v>18872</v>
       </c>
       <c r="C50" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B51" t="n">
-        <v>326.246</v>
+        <v>18902</v>
       </c>
       <c r="C51" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B52" t="n">
-        <v>327.232</v>
+        <v>18933</v>
       </c>
       <c r="C52" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B53" t="n">
-        <v>328.094</v>
+        <v>18963</v>
       </c>
       <c r="C53" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B54" t="n">
-        <v>329.048</v>
+        <v>18994</v>
       </c>
       <c r="C54" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45689</v>
-      </c>
-      <c r="B55" t="n">
-        <v>329.884</v>
+        <v>19025</v>
       </c>
       <c r="C55" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45717</v>
-      </c>
-      <c r="B56" t="n">
-        <v>330.766</v>
+        <v>19054</v>
       </c>
       <c r="C56" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B57" t="n">
-        <v>331.718</v>
+        <v>19085</v>
       </c>
       <c r="C57" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B58" t="n">
-        <v>332.258</v>
+        <v>19115</v>
       </c>
       <c r="C58" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45809</v>
-      </c>
-      <c r="B59" t="n">
-        <v>333.024</v>
+        <v>19146</v>
       </c>
       <c r="C59" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B60" t="n">
-        <v>333.763</v>
+        <v>19176</v>
       </c>
       <c r="C60" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B61" t="n">
-        <v>334.47</v>
+        <v>19207</v>
       </c>
       <c r="C61" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B62" t="n">
-        <v>335.25</v>
+        <v>19238</v>
       </c>
       <c r="C62" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="B63" t="n">
-        <v>336.389</v>
+        <v>19268</v>
       </c>
       <c r="C63" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B64" t="n">
-        <v>337.056</v>
+        <v>19299</v>
       </c>
       <c r="C64" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
+        <v>19329</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>19360</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>19391</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>19419</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>19450</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>19480</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>19511</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>19541</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>19572</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>19603</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>19633</v>
+      </c>
+      <c r="C75" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>19664</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>19694</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>19725</v>
+      </c>
+      <c r="C78" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>19756</v>
+      </c>
+      <c r="C79" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>19784</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>19815</v>
+      </c>
+      <c r="C81" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>19845</v>
+      </c>
+      <c r="C82" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>19876</v>
+      </c>
+      <c r="C83" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>19906</v>
+      </c>
+      <c r="C84" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>19937</v>
+      </c>
+      <c r="C85" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>19968</v>
+      </c>
+      <c r="C86" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>19998</v>
+      </c>
+      <c r="C87" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>20029</v>
+      </c>
+      <c r="C88" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>20059</v>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>20090</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>20121</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>20149</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>20180</v>
+      </c>
+      <c r="C93" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>20210</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>20241</v>
+      </c>
+      <c r="C95" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>20271</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>20302</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>20333</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>20363</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>20394</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>20424</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>20455</v>
+      </c>
+      <c r="C102" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>20486</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>20515</v>
+      </c>
+      <c r="C104" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>20546</v>
+      </c>
+      <c r="C105" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>20576</v>
+      </c>
+      <c r="C106" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>20607</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>20637</v>
+      </c>
+      <c r="C108" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>20668</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>20699</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>20729</v>
+      </c>
+      <c r="C111" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>20760</v>
+      </c>
+      <c r="C112" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>20790</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>20821</v>
+      </c>
+      <c r="C114" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>20852</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>20880</v>
+      </c>
+      <c r="C116" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>20911</v>
+      </c>
+      <c r="C117" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>20941</v>
+      </c>
+      <c r="C118" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>20972</v>
+      </c>
+      <c r="C119" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>21002</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>21033</v>
+      </c>
+      <c r="C121" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>21064</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>21094</v>
+      </c>
+      <c r="C123" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>21125</v>
+      </c>
+      <c r="C124" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>21155</v>
+      </c>
+      <c r="C125" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>21186</v>
+      </c>
+      <c r="C126" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>21217</v>
+      </c>
+      <c r="C127" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>21245</v>
+      </c>
+      <c r="C128" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>21276</v>
+      </c>
+      <c r="C129" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>21306</v>
+      </c>
+      <c r="C130" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>21337</v>
+      </c>
+      <c r="C131" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>21367</v>
+      </c>
+      <c r="C132" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>21398</v>
+      </c>
+      <c r="C133" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>21429</v>
+      </c>
+      <c r="C134" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>21459</v>
+      </c>
+      <c r="C135" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>21490</v>
+      </c>
+      <c r="C136" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>21520</v>
+      </c>
+      <c r="C137" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>21551</v>
+      </c>
+      <c r="C138" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>21582</v>
+      </c>
+      <c r="C139" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>21610</v>
+      </c>
+      <c r="C140" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>21641</v>
+      </c>
+      <c r="C141" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>21671</v>
+      </c>
+      <c r="C142" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>21702</v>
+      </c>
+      <c r="C143" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>21732</v>
+      </c>
+      <c r="C144" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>21763</v>
+      </c>
+      <c r="C145" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>21794</v>
+      </c>
+      <c r="C146" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>21824</v>
+      </c>
+      <c r="C147" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>21855</v>
+      </c>
+      <c r="C148" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>21885</v>
+      </c>
+      <c r="C149" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>21916</v>
+      </c>
+      <c r="C150" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>21947</v>
+      </c>
+      <c r="C151" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>21976</v>
+      </c>
+      <c r="C152" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>22007</v>
+      </c>
+      <c r="C153" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>22037</v>
+      </c>
+      <c r="C154" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>22068</v>
+      </c>
+      <c r="C155" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>22098</v>
+      </c>
+      <c r="C156" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>22129</v>
+      </c>
+      <c r="C157" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>22160</v>
+      </c>
+      <c r="C158" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>22190</v>
+      </c>
+      <c r="C159" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>22221</v>
+      </c>
+      <c r="C160" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>22251</v>
+      </c>
+      <c r="C161" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>22282</v>
+      </c>
+      <c r="C162" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>22313</v>
+      </c>
+      <c r="C163" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>22341</v>
+      </c>
+      <c r="C164" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>22372</v>
+      </c>
+      <c r="C165" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>22402</v>
+      </c>
+      <c r="C166" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>22433</v>
+      </c>
+      <c r="C167" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>22463</v>
+      </c>
+      <c r="C168" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>22494</v>
+      </c>
+      <c r="C169" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>22525</v>
+      </c>
+      <c r="C170" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>22555</v>
+      </c>
+      <c r="C171" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>22586</v>
+      </c>
+      <c r="C172" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>22616</v>
+      </c>
+      <c r="C173" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>22647</v>
+      </c>
+      <c r="C174" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>22678</v>
+      </c>
+      <c r="C175" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>22706</v>
+      </c>
+      <c r="C176" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>22737</v>
+      </c>
+      <c r="C177" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>22767</v>
+      </c>
+      <c r="C178" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>22798</v>
+      </c>
+      <c r="C179" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>22828</v>
+      </c>
+      <c r="C180" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>22859</v>
+      </c>
+      <c r="C181" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>22890</v>
+      </c>
+      <c r="C182" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>22920</v>
+      </c>
+      <c r="C183" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>22951</v>
+      </c>
+      <c r="C184" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>22981</v>
+      </c>
+      <c r="C185" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>23012</v>
+      </c>
+      <c r="C186" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>23043</v>
+      </c>
+      <c r="C187" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>23071</v>
+      </c>
+      <c r="C188" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>23102</v>
+      </c>
+      <c r="C189" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>23132</v>
+      </c>
+      <c r="C190" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>23163</v>
+      </c>
+      <c r="C191" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>23193</v>
+      </c>
+      <c r="C192" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>23224</v>
+      </c>
+      <c r="C193" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>23255</v>
+      </c>
+      <c r="C194" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>23285</v>
+      </c>
+      <c r="C195" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>23316</v>
+      </c>
+      <c r="C196" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>23346</v>
+      </c>
+      <c r="C197" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>23377</v>
+      </c>
+      <c r="C198" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>23408</v>
+      </c>
+      <c r="C199" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>23437</v>
+      </c>
+      <c r="C200" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>23468</v>
+      </c>
+      <c r="C201" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>23498</v>
+      </c>
+      <c r="C202" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>23529</v>
+      </c>
+      <c r="C203" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>23559</v>
+      </c>
+      <c r="C204" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>23590</v>
+      </c>
+      <c r="C205" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>23621</v>
+      </c>
+      <c r="C206" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>23651</v>
+      </c>
+      <c r="C207" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>23682</v>
+      </c>
+      <c r="C208" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>23712</v>
+      </c>
+      <c r="C209" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>23743</v>
+      </c>
+      <c r="C210" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>23774</v>
+      </c>
+      <c r="C211" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>23802</v>
+      </c>
+      <c r="C212" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>23833</v>
+      </c>
+      <c r="C213" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>23863</v>
+      </c>
+      <c r="C214" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>23894</v>
+      </c>
+      <c r="C215" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>23924</v>
+      </c>
+      <c r="C216" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>23955</v>
+      </c>
+      <c r="C217" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>23986</v>
+      </c>
+      <c r="C218" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>24016</v>
+      </c>
+      <c r="C219" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>24047</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>24077</v>
+      </c>
+      <c r="C221" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>24108</v>
+      </c>
+      <c r="C222" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>24139</v>
+      </c>
+      <c r="C223" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>24167</v>
+      </c>
+      <c r="C224" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>24198</v>
+      </c>
+      <c r="C225" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>24228</v>
+      </c>
+      <c r="C226" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>24259</v>
+      </c>
+      <c r="C227" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>24289</v>
+      </c>
+      <c r="C228" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>24320</v>
+      </c>
+      <c r="C229" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>24351</v>
+      </c>
+      <c r="C230" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>24381</v>
+      </c>
+      <c r="C231" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>24412</v>
+      </c>
+      <c r="C232" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>24442</v>
+      </c>
+      <c r="C233" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>24473</v>
+      </c>
+      <c r="C234" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>24504</v>
+      </c>
+      <c r="C235" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>24532</v>
+      </c>
+      <c r="C236" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>24563</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>24593</v>
+      </c>
+      <c r="C238" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>24624</v>
+      </c>
+      <c r="C239" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>24654</v>
+      </c>
+      <c r="C240" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>24685</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>24716</v>
+      </c>
+      <c r="C242" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>24746</v>
+      </c>
+      <c r="C243" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>24777</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>24807</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>24838</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>24869</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>24898</v>
+      </c>
+      <c r="C248" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>24929</v>
+      </c>
+      <c r="C249" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>24959</v>
+      </c>
+      <c r="C250" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>24990</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>25020</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>25051</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>25082</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>25112</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>25143</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>25173</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>25204</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>25235</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>25263</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>25294</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>25324</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>25355</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>25385</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>25416</v>
+      </c>
+      <c r="C265" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>25447</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>25477</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>25508</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>25538</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>25569</v>
+      </c>
+      <c r="C270" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>25600</v>
+      </c>
+      <c r="C271" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>25628</v>
+      </c>
+      <c r="C272" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>25659</v>
+      </c>
+      <c r="C273" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>25689</v>
+      </c>
+      <c r="C274" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>25720</v>
+      </c>
+      <c r="C275" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>25750</v>
+      </c>
+      <c r="C276" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>25781</v>
+      </c>
+      <c r="C277" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>25812</v>
+      </c>
+      <c r="C278" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>25842</v>
+      </c>
+      <c r="C279" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>25873</v>
+      </c>
+      <c r="C280" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>25903</v>
+      </c>
+      <c r="C281" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>25934</v>
+      </c>
+      <c r="C282" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>25965</v>
+      </c>
+      <c r="C283" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>25993</v>
+      </c>
+      <c r="C284" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>26024</v>
+      </c>
+      <c r="C285" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>26054</v>
+      </c>
+      <c r="C286" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>26085</v>
+      </c>
+      <c r="C287" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>26115</v>
+      </c>
+      <c r="C288" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>26146</v>
+      </c>
+      <c r="C289" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>26177</v>
+      </c>
+      <c r="C290" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>26207</v>
+      </c>
+      <c r="C291" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>26238</v>
+      </c>
+      <c r="C292" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>26268</v>
+      </c>
+      <c r="C293" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>26299</v>
+      </c>
+      <c r="C294" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>26330</v>
+      </c>
+      <c r="C295" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>26359</v>
+      </c>
+      <c r="C296" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>26390</v>
+      </c>
+      <c r="C297" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>26420</v>
+      </c>
+      <c r="C298" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>26451</v>
+      </c>
+      <c r="C299" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>26481</v>
+      </c>
+      <c r="C300" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>26512</v>
+      </c>
+      <c r="C301" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>26543</v>
+      </c>
+      <c r="C302" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>26573</v>
+      </c>
+      <c r="C303" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>26604</v>
+      </c>
+      <c r="C304" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>26634</v>
+      </c>
+      <c r="C305" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>26665</v>
+      </c>
+      <c r="C306" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>26696</v>
+      </c>
+      <c r="C307" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>26724</v>
+      </c>
+      <c r="C308" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>26755</v>
+      </c>
+      <c r="C309" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>26785</v>
+      </c>
+      <c r="C310" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>26816</v>
+      </c>
+      <c r="C311" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="n">
+        <v>26846</v>
+      </c>
+      <c r="C312" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="n">
+        <v>26877</v>
+      </c>
+      <c r="C313" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="n">
+        <v>26908</v>
+      </c>
+      <c r="C314" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>26938</v>
+      </c>
+      <c r="C315" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
+        <v>26969</v>
+      </c>
+      <c r="C316" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="n">
+        <v>26999</v>
+      </c>
+      <c r="C317" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>27030</v>
+      </c>
+      <c r="C318" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="n">
+        <v>27061</v>
+      </c>
+      <c r="C319" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="n">
+        <v>27089</v>
+      </c>
+      <c r="C320" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="n">
+        <v>27120</v>
+      </c>
+      <c r="C321" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="n">
+        <v>27150</v>
+      </c>
+      <c r="C322" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="n">
+        <v>27181</v>
+      </c>
+      <c r="C323" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="n">
+        <v>27211</v>
+      </c>
+      <c r="C324" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="n">
+        <v>27242</v>
+      </c>
+      <c r="C325" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="n">
+        <v>27273</v>
+      </c>
+      <c r="C326" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="n">
+        <v>27303</v>
+      </c>
+      <c r="C327" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="n">
+        <v>27334</v>
+      </c>
+      <c r="C328" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="n">
+        <v>27364</v>
+      </c>
+      <c r="C329" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="n">
+        <v>27395</v>
+      </c>
+      <c r="C330" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="n">
+        <v>27426</v>
+      </c>
+      <c r="C331" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="n">
+        <v>27454</v>
+      </c>
+      <c r="C332" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="n">
+        <v>27485</v>
+      </c>
+      <c r="C333" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="n">
+        <v>27515</v>
+      </c>
+      <c r="C334" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="n">
+        <v>27546</v>
+      </c>
+      <c r="C335" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="n">
+        <v>27576</v>
+      </c>
+      <c r="C336" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="n">
+        <v>27607</v>
+      </c>
+      <c r="C337" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="n">
+        <v>27638</v>
+      </c>
+      <c r="C338" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="n">
+        <v>27668</v>
+      </c>
+      <c r="C339" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="n">
+        <v>27699</v>
+      </c>
+      <c r="C340" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="n">
+        <v>27729</v>
+      </c>
+      <c r="C341" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="n">
+        <v>27760</v>
+      </c>
+      <c r="C342" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="n">
+        <v>27791</v>
+      </c>
+      <c r="C343" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="n">
+        <v>27820</v>
+      </c>
+      <c r="C344" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="n">
+        <v>27851</v>
+      </c>
+      <c r="C345" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="n">
+        <v>27881</v>
+      </c>
+      <c r="C346" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="n">
+        <v>27912</v>
+      </c>
+      <c r="C347" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="n">
+        <v>27942</v>
+      </c>
+      <c r="C348" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="n">
+        <v>27973</v>
+      </c>
+      <c r="C349" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="n">
+        <v>28004</v>
+      </c>
+      <c r="C350" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="n">
+        <v>28034</v>
+      </c>
+      <c r="C351" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="n">
+        <v>28065</v>
+      </c>
+      <c r="C352" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="n">
+        <v>28095</v>
+      </c>
+      <c r="C353" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="n">
+        <v>28126</v>
+      </c>
+      <c r="C354" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="n">
+        <v>28157</v>
+      </c>
+      <c r="C355" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="n">
+        <v>28185</v>
+      </c>
+      <c r="C356" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="n">
+        <v>28216</v>
+      </c>
+      <c r="C357" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="n">
+        <v>28246</v>
+      </c>
+      <c r="C358" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="n">
+        <v>28277</v>
+      </c>
+      <c r="C359" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="n">
+        <v>28307</v>
+      </c>
+      <c r="C360" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="n">
+        <v>28338</v>
+      </c>
+      <c r="C361" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="n">
+        <v>28369</v>
+      </c>
+      <c r="C362" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="n">
+        <v>28399</v>
+      </c>
+      <c r="C363" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="n">
+        <v>28430</v>
+      </c>
+      <c r="C364" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="n">
+        <v>28460</v>
+      </c>
+      <c r="C365" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="n">
+        <v>28491</v>
+      </c>
+      <c r="C366" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="n">
+        <v>28522</v>
+      </c>
+      <c r="C367" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="n">
+        <v>28550</v>
+      </c>
+      <c r="C368" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="n">
+        <v>28581</v>
+      </c>
+      <c r="C369" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="n">
+        <v>28611</v>
+      </c>
+      <c r="C370" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="n">
+        <v>28642</v>
+      </c>
+      <c r="C371" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="n">
+        <v>28672</v>
+      </c>
+      <c r="C372" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="n">
+        <v>28703</v>
+      </c>
+      <c r="C373" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="n">
+        <v>28734</v>
+      </c>
+      <c r="C374" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="n">
+        <v>28764</v>
+      </c>
+      <c r="C375" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="n">
+        <v>28795</v>
+      </c>
+      <c r="C376" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="n">
+        <v>28825</v>
+      </c>
+      <c r="C377" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="n">
+        <v>28856</v>
+      </c>
+      <c r="C378" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="n">
+        <v>28887</v>
+      </c>
+      <c r="C379" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="n">
+        <v>28915</v>
+      </c>
+      <c r="C380" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="n">
+        <v>28946</v>
+      </c>
+      <c r="C381" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="n">
+        <v>28976</v>
+      </c>
+      <c r="C382" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="n">
+        <v>29007</v>
+      </c>
+      <c r="C383" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="n">
+        <v>29037</v>
+      </c>
+      <c r="C384" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="n">
+        <v>29068</v>
+      </c>
+      <c r="C385" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="n">
+        <v>29099</v>
+      </c>
+      <c r="C386" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="n">
+        <v>29129</v>
+      </c>
+      <c r="C387" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="n">
+        <v>29160</v>
+      </c>
+      <c r="C388" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="n">
+        <v>29190</v>
+      </c>
+      <c r="C389" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="n">
+        <v>29221</v>
+      </c>
+      <c r="C390" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="n">
+        <v>29252</v>
+      </c>
+      <c r="C391" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="n">
+        <v>29281</v>
+      </c>
+      <c r="C392" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="n">
+        <v>29312</v>
+      </c>
+      <c r="C393" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="n">
+        <v>29342</v>
+      </c>
+      <c r="C394" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="n">
+        <v>29373</v>
+      </c>
+      <c r="C395" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="n">
+        <v>29403</v>
+      </c>
+      <c r="C396" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="n">
+        <v>29434</v>
+      </c>
+      <c r="C397" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="n">
+        <v>29465</v>
+      </c>
+      <c r="C398" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="n">
+        <v>29495</v>
+      </c>
+      <c r="C399" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="n">
+        <v>29526</v>
+      </c>
+      <c r="C400" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="n">
+        <v>29556</v>
+      </c>
+      <c r="C401" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="n">
+        <v>29587</v>
+      </c>
+      <c r="C402" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="n">
+        <v>29618</v>
+      </c>
+      <c r="C403" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="n">
+        <v>29646</v>
+      </c>
+      <c r="C404" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="n">
+        <v>29677</v>
+      </c>
+      <c r="C405" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="n">
+        <v>29707</v>
+      </c>
+      <c r="C406" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="C407" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="n">
+        <v>29768</v>
+      </c>
+      <c r="C408" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="n">
+        <v>29799</v>
+      </c>
+      <c r="C409" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="n">
+        <v>29830</v>
+      </c>
+      <c r="C410" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="n">
+        <v>29860</v>
+      </c>
+      <c r="C411" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="n">
+        <v>29891</v>
+      </c>
+      <c r="C412" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="n">
+        <v>29921</v>
+      </c>
+      <c r="C413" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="n">
+        <v>29952</v>
+      </c>
+      <c r="C414" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="n">
+        <v>29983</v>
+      </c>
+      <c r="C415" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="n">
+        <v>30011</v>
+      </c>
+      <c r="C416" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="n">
+        <v>30042</v>
+      </c>
+      <c r="C417" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="n">
+        <v>30072</v>
+      </c>
+      <c r="C418" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="n">
+        <v>30103</v>
+      </c>
+      <c r="C419" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>30133</v>
+      </c>
+      <c r="C420" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="n">
+        <v>30164</v>
+      </c>
+      <c r="C421" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>30195</v>
+      </c>
+      <c r="C422" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>30225</v>
+      </c>
+      <c r="C423" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>30256</v>
+      </c>
+      <c r="C424" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>30286</v>
+      </c>
+      <c r="C425" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>30317</v>
+      </c>
+      <c r="C426" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>30348</v>
+      </c>
+      <c r="C427" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>30376</v>
+      </c>
+      <c r="C428" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>30407</v>
+      </c>
+      <c r="C429" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>30437</v>
+      </c>
+      <c r="C430" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>30468</v>
+      </c>
+      <c r="C431" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>30498</v>
+      </c>
+      <c r="C432" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>30529</v>
+      </c>
+      <c r="C433" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>30560</v>
+      </c>
+      <c r="C434" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>30590</v>
+      </c>
+      <c r="C435" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>30621</v>
+      </c>
+      <c r="C436" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>30651</v>
+      </c>
+      <c r="C437" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>30682</v>
+      </c>
+      <c r="C438" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>30713</v>
+      </c>
+      <c r="C439" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>30742</v>
+      </c>
+      <c r="C440" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>30773</v>
+      </c>
+      <c r="C441" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>30803</v>
+      </c>
+      <c r="C442" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>30834</v>
+      </c>
+      <c r="C443" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>30864</v>
+      </c>
+      <c r="C444" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>30895</v>
+      </c>
+      <c r="C445" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="n">
+        <v>30926</v>
+      </c>
+      <c r="C446" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="n">
+        <v>30956</v>
+      </c>
+      <c r="C447" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="n">
+        <v>30987</v>
+      </c>
+      <c r="C448" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="n">
+        <v>31017</v>
+      </c>
+      <c r="C449" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="n">
+        <v>31048</v>
+      </c>
+      <c r="C450" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="n">
+        <v>31079</v>
+      </c>
+      <c r="C451" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="n">
+        <v>31107</v>
+      </c>
+      <c r="C452" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="n">
+        <v>31138</v>
+      </c>
+      <c r="C453" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="n">
+        <v>31168</v>
+      </c>
+      <c r="C454" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="n">
+        <v>31199</v>
+      </c>
+      <c r="C455" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="n">
+        <v>31229</v>
+      </c>
+      <c r="C456" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="n">
+        <v>31260</v>
+      </c>
+      <c r="C457" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="n">
+        <v>31291</v>
+      </c>
+      <c r="C458" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="n">
+        <v>31321</v>
+      </c>
+      <c r="C459" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="n">
+        <v>31352</v>
+      </c>
+      <c r="C460" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="n">
+        <v>31382</v>
+      </c>
+      <c r="C461" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="n">
+        <v>31413</v>
+      </c>
+      <c r="C462" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="n">
+        <v>31444</v>
+      </c>
+      <c r="C463" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="n">
+        <v>31472</v>
+      </c>
+      <c r="C464" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="n">
+        <v>31503</v>
+      </c>
+      <c r="C465" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="n">
+        <v>31533</v>
+      </c>
+      <c r="C466" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="n">
+        <v>31564</v>
+      </c>
+      <c r="C467" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="n">
+        <v>31594</v>
+      </c>
+      <c r="C468" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="n">
+        <v>31625</v>
+      </c>
+      <c r="C469" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="n">
+        <v>31656</v>
+      </c>
+      <c r="C470" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="n">
+        <v>31686</v>
+      </c>
+      <c r="C471" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="n">
+        <v>31717</v>
+      </c>
+      <c r="C472" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="n">
+        <v>31747</v>
+      </c>
+      <c r="C473" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>31778</v>
+      </c>
+      <c r="C474" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>31809</v>
+      </c>
+      <c r="C475" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="n">
+        <v>31837</v>
+      </c>
+      <c r="C476" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="n">
+        <v>31868</v>
+      </c>
+      <c r="C477" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="n">
+        <v>31898</v>
+      </c>
+      <c r="C478" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="n">
+        <v>31929</v>
+      </c>
+      <c r="C479" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="n">
+        <v>31959</v>
+      </c>
+      <c r="C480" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="n">
+        <v>31990</v>
+      </c>
+      <c r="C481" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="n">
+        <v>32021</v>
+      </c>
+      <c r="C482" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="n">
+        <v>32051</v>
+      </c>
+      <c r="C483" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="n">
+        <v>32082</v>
+      </c>
+      <c r="C484" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="n">
+        <v>32112</v>
+      </c>
+      <c r="C485" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="n">
+        <v>32143</v>
+      </c>
+      <c r="C486" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="n">
+        <v>32174</v>
+      </c>
+      <c r="C487" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="n">
+        <v>32203</v>
+      </c>
+      <c r="C488" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="n">
+        <v>32234</v>
+      </c>
+      <c r="C489" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="n">
+        <v>32264</v>
+      </c>
+      <c r="C490" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="n">
+        <v>32295</v>
+      </c>
+      <c r="C491" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="n">
+        <v>32325</v>
+      </c>
+      <c r="C492" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="n">
+        <v>32356</v>
+      </c>
+      <c r="C493" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="n">
+        <v>32387</v>
+      </c>
+      <c r="C494" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="n">
+        <v>32417</v>
+      </c>
+      <c r="C495" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="n">
+        <v>32448</v>
+      </c>
+      <c r="C496" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="n">
+        <v>32478</v>
+      </c>
+      <c r="C497" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="n">
+        <v>32509</v>
+      </c>
+      <c r="C498" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="n">
+        <v>32540</v>
+      </c>
+      <c r="C499" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="n">
+        <v>32568</v>
+      </c>
+      <c r="C500" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="n">
+        <v>32599</v>
+      </c>
+      <c r="C501" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="n">
+        <v>32629</v>
+      </c>
+      <c r="C502" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="n">
+        <v>32660</v>
+      </c>
+      <c r="C503" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="n">
+        <v>32690</v>
+      </c>
+      <c r="C504" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="n">
+        <v>32721</v>
+      </c>
+      <c r="C505" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="n">
+        <v>32752</v>
+      </c>
+      <c r="C506" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n">
+        <v>32782</v>
+      </c>
+      <c r="C507" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n">
+        <v>32813</v>
+      </c>
+      <c r="C508" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="n">
+        <v>32843</v>
+      </c>
+      <c r="C509" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="n">
+        <v>32874</v>
+      </c>
+      <c r="C510" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n">
+        <v>32905</v>
+      </c>
+      <c r="C511" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n">
+        <v>32933</v>
+      </c>
+      <c r="C512" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n">
+        <v>32964</v>
+      </c>
+      <c r="C513" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n">
+        <v>32994</v>
+      </c>
+      <c r="C514" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n">
+        <v>33025</v>
+      </c>
+      <c r="C515" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="n">
+        <v>33055</v>
+      </c>
+      <c r="C516" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="n">
+        <v>33086</v>
+      </c>
+      <c r="C517" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="n">
+        <v>33117</v>
+      </c>
+      <c r="C518" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="n">
+        <v>33147</v>
+      </c>
+      <c r="C519" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="n">
+        <v>33178</v>
+      </c>
+      <c r="C520" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="n">
+        <v>33208</v>
+      </c>
+      <c r="C521" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="n">
+        <v>33239</v>
+      </c>
+      <c r="C522" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="n">
+        <v>33270</v>
+      </c>
+      <c r="C523" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="n">
+        <v>33298</v>
+      </c>
+      <c r="C524" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="n">
+        <v>33329</v>
+      </c>
+      <c r="C525" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="n">
+        <v>33359</v>
+      </c>
+      <c r="C526" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="n">
+        <v>33390</v>
+      </c>
+      <c r="C527" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="n">
+        <v>33420</v>
+      </c>
+      <c r="C528" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="n">
+        <v>33451</v>
+      </c>
+      <c r="C529" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="n">
+        <v>33482</v>
+      </c>
+      <c r="C530" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="n">
+        <v>33512</v>
+      </c>
+      <c r="C531" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="n">
+        <v>33543</v>
+      </c>
+      <c r="C532" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="n">
+        <v>33573</v>
+      </c>
+      <c r="C533" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="n">
+        <v>33604</v>
+      </c>
+      <c r="C534" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="n">
+        <v>33635</v>
+      </c>
+      <c r="C535" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="n">
+        <v>33664</v>
+      </c>
+      <c r="C536" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="n">
+        <v>33695</v>
+      </c>
+      <c r="C537" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="n">
+        <v>33725</v>
+      </c>
+      <c r="C538" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="n">
+        <v>33756</v>
+      </c>
+      <c r="C539" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="n">
+        <v>33786</v>
+      </c>
+      <c r="C540" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="n">
+        <v>33817</v>
+      </c>
+      <c r="C541" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="n">
+        <v>33848</v>
+      </c>
+      <c r="C542" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="n">
+        <v>33878</v>
+      </c>
+      <c r="C543" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="n">
+        <v>33909</v>
+      </c>
+      <c r="C544" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="n">
+        <v>33939</v>
+      </c>
+      <c r="C545" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="n">
+        <v>33970</v>
+      </c>
+      <c r="C546" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="n">
+        <v>34001</v>
+      </c>
+      <c r="C547" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="n">
+        <v>34029</v>
+      </c>
+      <c r="C548" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="n">
+        <v>34060</v>
+      </c>
+      <c r="C549" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="n">
+        <v>34090</v>
+      </c>
+      <c r="C550" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="n">
+        <v>34121</v>
+      </c>
+      <c r="C551" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="n">
+        <v>34151</v>
+      </c>
+      <c r="C552" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="n">
+        <v>34182</v>
+      </c>
+      <c r="C553" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="n">
+        <v>34213</v>
+      </c>
+      <c r="C554" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="n">
+        <v>34243</v>
+      </c>
+      <c r="C555" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="n">
+        <v>34274</v>
+      </c>
+      <c r="C556" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="n">
+        <v>34304</v>
+      </c>
+      <c r="C557" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="n">
+        <v>34335</v>
+      </c>
+      <c r="C558" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="n">
+        <v>34366</v>
+      </c>
+      <c r="C559" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="n">
+        <v>34394</v>
+      </c>
+      <c r="C560" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="n">
+        <v>34425</v>
+      </c>
+      <c r="C561" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="n">
+        <v>34455</v>
+      </c>
+      <c r="C562" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="n">
+        <v>34486</v>
+      </c>
+      <c r="C563" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="n">
+        <v>34516</v>
+      </c>
+      <c r="C564" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="n">
+        <v>34547</v>
+      </c>
+      <c r="C565" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="n">
+        <v>34578</v>
+      </c>
+      <c r="C566" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="n">
+        <v>34608</v>
+      </c>
+      <c r="C567" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="n">
+        <v>34639</v>
+      </c>
+      <c r="C568" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="n">
+        <v>34669</v>
+      </c>
+      <c r="C569" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="n">
+        <v>34700</v>
+      </c>
+      <c r="C570" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="n">
+        <v>34731</v>
+      </c>
+      <c r="C571" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="n">
+        <v>34759</v>
+      </c>
+      <c r="C572" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="n">
+        <v>34790</v>
+      </c>
+      <c r="C573" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="n">
+        <v>34820</v>
+      </c>
+      <c r="C574" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>34851</v>
+      </c>
+      <c r="C575" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>34881</v>
+      </c>
+      <c r="C576" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>34912</v>
+      </c>
+      <c r="C577" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>34943</v>
+      </c>
+      <c r="C578" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>34973</v>
+      </c>
+      <c r="C579" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>35004</v>
+      </c>
+      <c r="C580" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>35034</v>
+      </c>
+      <c r="C581" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>35065</v>
+      </c>
+      <c r="C582" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>35096</v>
+      </c>
+      <c r="C583" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>35125</v>
+      </c>
+      <c r="C584" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="n">
+        <v>35156</v>
+      </c>
+      <c r="C585" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="n">
+        <v>35186</v>
+      </c>
+      <c r="C586" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>35217</v>
+      </c>
+      <c r="C587" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>35247</v>
+      </c>
+      <c r="C588" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n">
+        <v>35278</v>
+      </c>
+      <c r="C589" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>35309</v>
+      </c>
+      <c r="C590" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n">
+        <v>35339</v>
+      </c>
+      <c r="C591" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n">
+        <v>35370</v>
+      </c>
+      <c r="C592" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n">
+        <v>35400</v>
+      </c>
+      <c r="C593" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n">
+        <v>35431</v>
+      </c>
+      <c r="C594" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n">
+        <v>35462</v>
+      </c>
+      <c r="C595" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n">
+        <v>35490</v>
+      </c>
+      <c r="C596" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="n">
+        <v>35521</v>
+      </c>
+      <c r="C597" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="n">
+        <v>35551</v>
+      </c>
+      <c r="C598" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="n">
+        <v>35582</v>
+      </c>
+      <c r="C599" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="n">
+        <v>35612</v>
+      </c>
+      <c r="C600" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="n">
+        <v>35643</v>
+      </c>
+      <c r="C601" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="n">
+        <v>35674</v>
+      </c>
+      <c r="C602" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>35704</v>
+      </c>
+      <c r="C603" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>35735</v>
+      </c>
+      <c r="C604" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>35765</v>
+      </c>
+      <c r="C605" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>35796</v>
+      </c>
+      <c r="C606" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="n">
+        <v>35827</v>
+      </c>
+      <c r="C607" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="n">
+        <v>35855</v>
+      </c>
+      <c r="C608" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="n">
+        <v>35886</v>
+      </c>
+      <c r="C609" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>35916</v>
+      </c>
+      <c r="C610" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>35947</v>
+      </c>
+      <c r="C611" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="n">
+        <v>35977</v>
+      </c>
+      <c r="C612" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="n">
+        <v>36008</v>
+      </c>
+      <c r="C613" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>36039</v>
+      </c>
+      <c r="C614" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="n">
+        <v>36069</v>
+      </c>
+      <c r="C615" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="n">
+        <v>36100</v>
+      </c>
+      <c r="C616" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="n">
+        <v>36130</v>
+      </c>
+      <c r="C617" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="n">
+        <v>36161</v>
+      </c>
+      <c r="C618" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="n">
+        <v>36192</v>
+      </c>
+      <c r="C619" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="n">
+        <v>36220</v>
+      </c>
+      <c r="C620" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="n">
+        <v>36251</v>
+      </c>
+      <c r="C621" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="n">
+        <v>36281</v>
+      </c>
+      <c r="C622" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="n">
+        <v>36312</v>
+      </c>
+      <c r="C623" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="n">
+        <v>36342</v>
+      </c>
+      <c r="C624" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="n">
+        <v>36373</v>
+      </c>
+      <c r="C625" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="n">
+        <v>36404</v>
+      </c>
+      <c r="C626" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="n">
+        <v>36434</v>
+      </c>
+      <c r="C627" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="n">
+        <v>36465</v>
+      </c>
+      <c r="C628" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="n">
+        <v>36495</v>
+      </c>
+      <c r="C629" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="n">
+        <v>36526</v>
+      </c>
+      <c r="C630" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="n">
+        <v>36557</v>
+      </c>
+      <c r="C631" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="n">
+        <v>36586</v>
+      </c>
+      <c r="C632" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="n">
+        <v>36617</v>
+      </c>
+      <c r="C633" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="n">
+        <v>36647</v>
+      </c>
+      <c r="C634" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="n">
+        <v>36678</v>
+      </c>
+      <c r="C635" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="n">
+        <v>36708</v>
+      </c>
+      <c r="C636" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="n">
+        <v>36739</v>
+      </c>
+      <c r="C637" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="n">
+        <v>36770</v>
+      </c>
+      <c r="C638" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="n">
+        <v>36800</v>
+      </c>
+      <c r="C639" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="n">
+        <v>36831</v>
+      </c>
+      <c r="C640" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="n">
+        <v>36861</v>
+      </c>
+      <c r="C641" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="n">
+        <v>36892</v>
+      </c>
+      <c r="C642" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="n">
+        <v>36923</v>
+      </c>
+      <c r="C643" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="n">
+        <v>36951</v>
+      </c>
+      <c r="C644" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="n">
+        <v>36982</v>
+      </c>
+      <c r="C645" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="n">
+        <v>37012</v>
+      </c>
+      <c r="C646" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="n">
+        <v>37043</v>
+      </c>
+      <c r="C647" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="n">
+        <v>37073</v>
+      </c>
+      <c r="C648" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="n">
+        <v>37104</v>
+      </c>
+      <c r="C649" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="n">
+        <v>37135</v>
+      </c>
+      <c r="C650" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="n">
+        <v>37165</v>
+      </c>
+      <c r="C651" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="n">
+        <v>37196</v>
+      </c>
+      <c r="C652" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="n">
+        <v>37226</v>
+      </c>
+      <c r="C653" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="n">
+        <v>37257</v>
+      </c>
+      <c r="C654" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="n">
+        <v>37288</v>
+      </c>
+      <c r="C655" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="n">
+        <v>37316</v>
+      </c>
+      <c r="C656" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="n">
+        <v>37347</v>
+      </c>
+      <c r="C657" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="n">
+        <v>37377</v>
+      </c>
+      <c r="C658" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="n">
+        <v>37408</v>
+      </c>
+      <c r="C659" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="n">
+        <v>37438</v>
+      </c>
+      <c r="C660" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="n">
+        <v>37469</v>
+      </c>
+      <c r="C661" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="n">
+        <v>37500</v>
+      </c>
+      <c r="C662" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="n">
+        <v>37530</v>
+      </c>
+      <c r="C663" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="n">
+        <v>37561</v>
+      </c>
+      <c r="C664" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="n">
+        <v>37591</v>
+      </c>
+      <c r="C665" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="n">
+        <v>37622</v>
+      </c>
+      <c r="C666" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="n">
+        <v>37653</v>
+      </c>
+      <c r="C667" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>37681</v>
+      </c>
+      <c r="C668" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="n">
+        <v>37712</v>
+      </c>
+      <c r="C669" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>37742</v>
+      </c>
+      <c r="C670" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>37773</v>
+      </c>
+      <c r="C671" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
+        <v>37803</v>
+      </c>
+      <c r="C672" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
+        <v>37834</v>
+      </c>
+      <c r="C673" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="n">
+        <v>37865</v>
+      </c>
+      <c r="C674" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="n">
+        <v>37895</v>
+      </c>
+      <c r="C675" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="n">
+        <v>37926</v>
+      </c>
+      <c r="C676" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="n">
+        <v>37956</v>
+      </c>
+      <c r="C677" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="n">
+        <v>37987</v>
+      </c>
+      <c r="C678" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="n">
+        <v>38018</v>
+      </c>
+      <c r="C679" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="n">
+        <v>38047</v>
+      </c>
+      <c r="C680" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n">
+        <v>38078</v>
+      </c>
+      <c r="C681" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="n">
+        <v>38108</v>
+      </c>
+      <c r="C682" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="n">
+        <v>38139</v>
+      </c>
+      <c r="C683" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>38169</v>
+      </c>
+      <c r="C684" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
+        <v>38200</v>
+      </c>
+      <c r="C685" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n">
+        <v>38231</v>
+      </c>
+      <c r="C686" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n">
+        <v>38261</v>
+      </c>
+      <c r="C687" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="n">
+        <v>38292</v>
+      </c>
+      <c r="C688" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="n">
+        <v>38322</v>
+      </c>
+      <c r="C689" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="n">
+        <v>38353</v>
+      </c>
+      <c r="C690" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="n">
+        <v>38384</v>
+      </c>
+      <c r="C691" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="n">
+        <v>38412</v>
+      </c>
+      <c r="C692" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="n">
+        <v>38443</v>
+      </c>
+      <c r="C693" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="n">
+        <v>38473</v>
+      </c>
+      <c r="C694" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="n">
+        <v>38504</v>
+      </c>
+      <c r="C695" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="n">
+        <v>38534</v>
+      </c>
+      <c r="C696" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="n">
+        <v>38565</v>
+      </c>
+      <c r="C697" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="n">
+        <v>38596</v>
+      </c>
+      <c r="C698" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="n">
+        <v>38626</v>
+      </c>
+      <c r="C699" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="n">
+        <v>38657</v>
+      </c>
+      <c r="C700" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="n">
+        <v>38687</v>
+      </c>
+      <c r="C701" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="n">
+        <v>38718</v>
+      </c>
+      <c r="C702" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="n">
+        <v>38749</v>
+      </c>
+      <c r="C703" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="n">
+        <v>38777</v>
+      </c>
+      <c r="C704" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="n">
+        <v>38808</v>
+      </c>
+      <c r="C705" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="n">
+        <v>38838</v>
+      </c>
+      <c r="C706" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="n">
+        <v>38869</v>
+      </c>
+      <c r="C707" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="n">
+        <v>38899</v>
+      </c>
+      <c r="C708" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="n">
+        <v>38930</v>
+      </c>
+      <c r="C709" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="n">
+        <v>38961</v>
+      </c>
+      <c r="C710" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="n">
+        <v>38991</v>
+      </c>
+      <c r="C711" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="n">
+        <v>39022</v>
+      </c>
+      <c r="C712" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="n">
+        <v>39052</v>
+      </c>
+      <c r="C713" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="n">
+        <v>39083</v>
+      </c>
+      <c r="C714" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="n">
+        <v>39114</v>
+      </c>
+      <c r="C715" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="n">
+        <v>39142</v>
+      </c>
+      <c r="C716" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="n">
+        <v>39173</v>
+      </c>
+      <c r="C717" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="n">
+        <v>39203</v>
+      </c>
+      <c r="C718" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="n">
+        <v>39234</v>
+      </c>
+      <c r="C719" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="n">
+        <v>39264</v>
+      </c>
+      <c r="C720" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="n">
+        <v>39295</v>
+      </c>
+      <c r="C721" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="n">
+        <v>39326</v>
+      </c>
+      <c r="C722" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="1" t="n">
+        <v>39356</v>
+      </c>
+      <c r="C723" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="n">
+        <v>39387</v>
+      </c>
+      <c r="C724" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="n">
+        <v>39417</v>
+      </c>
+      <c r="C725" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="n">
+        <v>39448</v>
+      </c>
+      <c r="C726" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="n">
+        <v>39479</v>
+      </c>
+      <c r="C727" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="n">
+        <v>39508</v>
+      </c>
+      <c r="C728" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="n">
+        <v>39539</v>
+      </c>
+      <c r="C729" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="n">
+        <v>39569</v>
+      </c>
+      <c r="C730" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="n">
+        <v>39600</v>
+      </c>
+      <c r="C731" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="n">
+        <v>39630</v>
+      </c>
+      <c r="C732" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="n">
+        <v>39661</v>
+      </c>
+      <c r="C733" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="C734" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="n">
+        <v>39722</v>
+      </c>
+      <c r="C735" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="n">
+        <v>39753</v>
+      </c>
+      <c r="C736" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="n">
+        <v>39783</v>
+      </c>
+      <c r="C737" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="n">
+        <v>39814</v>
+      </c>
+      <c r="C738" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="n">
+        <v>39845</v>
+      </c>
+      <c r="C739" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="n">
+        <v>39873</v>
+      </c>
+      <c r="C740" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="n">
+        <v>39904</v>
+      </c>
+      <c r="C741" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="n">
+        <v>39934</v>
+      </c>
+      <c r="C742" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="n">
+        <v>39965</v>
+      </c>
+      <c r="C743" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="n">
+        <v>39995</v>
+      </c>
+      <c r="C744" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="n">
+        <v>40026</v>
+      </c>
+      <c r="C745" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="n">
+        <v>40057</v>
+      </c>
+      <c r="C746" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="n">
+        <v>40087</v>
+      </c>
+      <c r="C747" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="n">
+        <v>40118</v>
+      </c>
+      <c r="C748" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="n">
+        <v>40148</v>
+      </c>
+      <c r="C749" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="n">
+        <v>40179</v>
+      </c>
+      <c r="C750" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="n">
+        <v>40210</v>
+      </c>
+      <c r="C751" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="n">
+        <v>40238</v>
+      </c>
+      <c r="C752" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="n">
+        <v>40269</v>
+      </c>
+      <c r="C753" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="n">
+        <v>40299</v>
+      </c>
+      <c r="C754" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="n">
+        <v>40330</v>
+      </c>
+      <c r="C755" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="n">
+        <v>40360</v>
+      </c>
+      <c r="C756" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="n">
+        <v>40391</v>
+      </c>
+      <c r="C757" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="n">
+        <v>40422</v>
+      </c>
+      <c r="C758" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="n">
+        <v>40452</v>
+      </c>
+      <c r="C759" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="n">
+        <v>40483</v>
+      </c>
+      <c r="C760" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="n">
+        <v>40513</v>
+      </c>
+      <c r="C761" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="n">
+        <v>40544</v>
+      </c>
+      <c r="C762" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="n">
+        <v>40575</v>
+      </c>
+      <c r="C763" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="n">
+        <v>40603</v>
+      </c>
+      <c r="C764" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="n">
+        <v>40634</v>
+      </c>
+      <c r="C765" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="1" t="n">
+        <v>40664</v>
+      </c>
+      <c r="C766" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="n">
+        <v>40695</v>
+      </c>
+      <c r="C767" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="n">
+        <v>40725</v>
+      </c>
+      <c r="C768" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="1" t="n">
+        <v>40756</v>
+      </c>
+      <c r="C769" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="1" t="n">
+        <v>40787</v>
+      </c>
+      <c r="C770" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="1" t="n">
+        <v>40817</v>
+      </c>
+      <c r="C771" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="1" t="n">
+        <v>40848</v>
+      </c>
+      <c r="C772" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="1" t="n">
+        <v>40878</v>
+      </c>
+      <c r="C773" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="1" t="n">
+        <v>40909</v>
+      </c>
+      <c r="C774" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="1" t="n">
+        <v>40940</v>
+      </c>
+      <c r="C775" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="1" t="n">
+        <v>40969</v>
+      </c>
+      <c r="C776" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="1" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C777" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="1" t="n">
+        <v>41030</v>
+      </c>
+      <c r="C778" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="1" t="n">
+        <v>41061</v>
+      </c>
+      <c r="C779" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="1" t="n">
+        <v>41091</v>
+      </c>
+      <c r="C780" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="1" t="n">
+        <v>41122</v>
+      </c>
+      <c r="C781" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="1" t="n">
+        <v>41153</v>
+      </c>
+      <c r="C782" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="1" t="n">
+        <v>41183</v>
+      </c>
+      <c r="C783" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="1" t="n">
+        <v>41214</v>
+      </c>
+      <c r="C784" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="1" t="n">
+        <v>41244</v>
+      </c>
+      <c r="C785" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="1" t="n">
+        <v>41275</v>
+      </c>
+      <c r="C786" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="n">
+        <v>41306</v>
+      </c>
+      <c r="C787" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>41334</v>
+      </c>
+      <c r="C788" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>41365</v>
+      </c>
+      <c r="C789" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>41395</v>
+      </c>
+      <c r="C790" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>41426</v>
+      </c>
+      <c r="C791" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>41456</v>
+      </c>
+      <c r="C792" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="1" t="n">
+        <v>41487</v>
+      </c>
+      <c r="C793" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="1" t="n">
+        <v>41518</v>
+      </c>
+      <c r="C794" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>41548</v>
+      </c>
+      <c r="C795" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>41579</v>
+      </c>
+      <c r="C796" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>41609</v>
+      </c>
+      <c r="C797" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>41640</v>
+      </c>
+      <c r="C798" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="1" t="n">
+        <v>41671</v>
+      </c>
+      <c r="C799" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="1" t="n">
+        <v>41699</v>
+      </c>
+      <c r="C800" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="1" t="n">
+        <v>41730</v>
+      </c>
+      <c r="C801" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="1" t="n">
+        <v>41760</v>
+      </c>
+      <c r="C802" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="1" t="n">
+        <v>41791</v>
+      </c>
+      <c r="C803" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="1" t="n">
+        <v>41821</v>
+      </c>
+      <c r="C804" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>41852</v>
+      </c>
+      <c r="C805" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>41883</v>
+      </c>
+      <c r="C806" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>41913</v>
+      </c>
+      <c r="C807" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>41944</v>
+      </c>
+      <c r="C808" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>41974</v>
+      </c>
+      <c r="C809" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="n">
+        <v>42005</v>
+      </c>
+      <c r="C810" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>42036</v>
+      </c>
+      <c r="C811" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>42064</v>
+      </c>
+      <c r="C812" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>42095</v>
+      </c>
+      <c r="C813" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>42125</v>
+      </c>
+      <c r="C814" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>42156</v>
+      </c>
+      <c r="C815" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="1" t="n">
+        <v>42186</v>
+      </c>
+      <c r="C816" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="1" t="n">
+        <v>42217</v>
+      </c>
+      <c r="C817" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="n">
+        <v>42248</v>
+      </c>
+      <c r="C818" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="n">
+        <v>42278</v>
+      </c>
+      <c r="C819" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="1" t="n">
+        <v>42309</v>
+      </c>
+      <c r="C820" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="C821" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="n">
+        <v>42370</v>
+      </c>
+      <c r="C822" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="n">
+        <v>42401</v>
+      </c>
+      <c r="C823" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="n">
+        <v>42430</v>
+      </c>
+      <c r="C824" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="n">
+        <v>42461</v>
+      </c>
+      <c r="C825" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="1" t="n">
+        <v>42491</v>
+      </c>
+      <c r="C826" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="1" t="n">
+        <v>42522</v>
+      </c>
+      <c r="C827" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="1" t="n">
+        <v>42552</v>
+      </c>
+      <c r="C828" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="1" t="n">
+        <v>42583</v>
+      </c>
+      <c r="C829" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="1" t="n">
+        <v>42614</v>
+      </c>
+      <c r="C830" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="n">
+        <v>42644</v>
+      </c>
+      <c r="C831" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="1" t="n">
+        <v>42675</v>
+      </c>
+      <c r="C832" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="C833" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="n">
+        <v>42736</v>
+      </c>
+      <c r="C834" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="1" t="n">
+        <v>42767</v>
+      </c>
+      <c r="C835" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="1" t="n">
+        <v>42795</v>
+      </c>
+      <c r="C836" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="1" t="n">
+        <v>42826</v>
+      </c>
+      <c r="C837" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="1" t="n">
+        <v>42856</v>
+      </c>
+      <c r="C838" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="1" t="n">
+        <v>42887</v>
+      </c>
+      <c r="C839" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="1" t="n">
+        <v>42917</v>
+      </c>
+      <c r="C840" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="1" t="n">
+        <v>42948</v>
+      </c>
+      <c r="C841" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="1" t="n">
+        <v>42979</v>
+      </c>
+      <c r="C842" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="1" t="n">
+        <v>43009</v>
+      </c>
+      <c r="C843" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="1" t="n">
+        <v>43040</v>
+      </c>
+      <c r="C844" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="C845" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="1" t="n">
+        <v>43101</v>
+      </c>
+      <c r="C846" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="1" t="n">
+        <v>43132</v>
+      </c>
+      <c r="C847" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="C848" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="1" t="n">
+        <v>43191</v>
+      </c>
+      <c r="C849" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="1" t="n">
+        <v>43221</v>
+      </c>
+      <c r="C850" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="1" t="n">
+        <v>43252</v>
+      </c>
+      <c r="C851" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="1" t="n">
+        <v>43282</v>
+      </c>
+      <c r="C852" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="1" t="n">
+        <v>43313</v>
+      </c>
+      <c r="C853" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="1" t="n">
+        <v>43344</v>
+      </c>
+      <c r="C854" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="1" t="n">
+        <v>43374</v>
+      </c>
+      <c r="C855" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="1" t="n">
+        <v>43405</v>
+      </c>
+      <c r="C856" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="C857" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="1" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C858" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="1" t="n">
+        <v>43497</v>
+      </c>
+      <c r="C859" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="1" t="n">
+        <v>43525</v>
+      </c>
+      <c r="C860" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="1" t="n">
+        <v>43556</v>
+      </c>
+      <c r="C861" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="1" t="n">
+        <v>43586</v>
+      </c>
+      <c r="C862" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="1" t="n">
+        <v>43617</v>
+      </c>
+      <c r="C863" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="1" t="n">
+        <v>43647</v>
+      </c>
+      <c r="C864" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="1" t="n">
+        <v>43678</v>
+      </c>
+      <c r="C865" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="1" t="n">
+        <v>43709</v>
+      </c>
+      <c r="C866" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="1" t="n">
+        <v>43739</v>
+      </c>
+      <c r="C867" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="1" t="n">
+        <v>43770</v>
+      </c>
+      <c r="C868" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="1" t="n">
+        <v>43800</v>
+      </c>
+      <c r="C869" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C870" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="C871" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="1" t="n">
+        <v>43891</v>
+      </c>
+      <c r="C872" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="1" t="n">
+        <v>43922</v>
+      </c>
+      <c r="C873" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="1" t="n">
+        <v>43952</v>
+      </c>
+      <c r="C874" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="1" t="n">
+        <v>43983</v>
+      </c>
+      <c r="C875" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="1" t="n">
+        <v>44013</v>
+      </c>
+      <c r="C876" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="1" t="n">
+        <v>44044</v>
+      </c>
+      <c r="C877" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="1" t="n">
+        <v>44075</v>
+      </c>
+      <c r="C878" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="1" t="n">
+        <v>44105</v>
+      </c>
+      <c r="C879" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="1" t="n">
+        <v>44136</v>
+      </c>
+      <c r="C880" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="C881" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B882" t="n">
+        <v>262.687</v>
+      </c>
+      <c r="C882" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="1" t="n">
+        <v>44228</v>
+      </c>
+      <c r="B883" t="n">
+        <v>263.579</v>
+      </c>
+      <c r="C883" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B884" t="n">
+        <v>264.961</v>
+      </c>
+      <c r="C884" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="1" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B885" t="n">
+        <v>266.614</v>
+      </c>
+      <c r="C885" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="1" t="n">
+        <v>44317</v>
+      </c>
+      <c r="B886" t="n">
+        <v>268.383</v>
+      </c>
+      <c r="C886" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B887" t="n">
+        <v>270.654</v>
+      </c>
+      <c r="C887" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="1" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B888" t="n">
+        <v>271.903</v>
+      </c>
+      <c r="C888" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="1" t="n">
+        <v>44409</v>
+      </c>
+      <c r="B889" t="n">
+        <v>272.676</v>
+      </c>
+      <c r="C889" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B890" t="n">
+        <v>273.91</v>
+      </c>
+      <c r="C890" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="1" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B891" t="n">
+        <v>276.55</v>
+      </c>
+      <c r="C891" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="1" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B892" t="n">
+        <v>278.919</v>
+      </c>
+      <c r="C892" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B893" t="n">
+        <v>280.845</v>
+      </c>
+      <c r="C893" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B894" t="n">
+        <v>282.543</v>
+      </c>
+      <c r="C894" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B895" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="C895" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B896" t="n">
+        <v>287.674</v>
+      </c>
+      <c r="C896" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="1" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B897" t="n">
+        <v>288.561</v>
+      </c>
+      <c r="C897" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B898" t="n">
+        <v>291.298</v>
+      </c>
+      <c r="C898" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B899" t="n">
+        <v>294.957</v>
+      </c>
+      <c r="C899" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="1" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B900" t="n">
+        <v>294.913</v>
+      </c>
+      <c r="C900" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B901" t="n">
+        <v>295.097</v>
+      </c>
+      <c r="C901" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B902" t="n">
+        <v>296.349</v>
+      </c>
+      <c r="C902" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="1" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B903" t="n">
+        <v>298.007</v>
+      </c>
+      <c r="C903" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B904" t="n">
+        <v>298.786</v>
+      </c>
+      <c r="C904" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B905" t="n">
+        <v>298.832</v>
+      </c>
+      <c r="C905" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B906" t="n">
+        <v>300.42</v>
+      </c>
+      <c r="C906" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="1" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B907" t="n">
+        <v>301.45</v>
+      </c>
+      <c r="C907" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B908" t="n">
+        <v>301.821</v>
+      </c>
+      <c r="C908" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B909" t="n">
+        <v>302.845</v>
+      </c>
+      <c r="C909" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="1" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B910" t="n">
+        <v>303.334</v>
+      </c>
+      <c r="C910" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B911" t="n">
+        <v>304.014</v>
+      </c>
+      <c r="C911" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B912" t="n">
+        <v>304.609</v>
+      </c>
+      <c r="C912" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B913" t="n">
+        <v>306.082</v>
+      </c>
+      <c r="C913" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B914" t="n">
+        <v>307.276</v>
+      </c>
+      <c r="C914" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B915" t="n">
+        <v>307.696</v>
+      </c>
+      <c r="C915" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B916" t="n">
+        <v>308.148</v>
+      </c>
+      <c r="C916" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B917" t="n">
+        <v>308.741</v>
+      </c>
+      <c r="C917" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B918" t="n">
+        <v>309.698</v>
+      </c>
+      <c r="C918" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B919" t="n">
+        <v>310.967</v>
+      </c>
+      <c r="C919" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B920" t="n">
+        <v>312.345</v>
+      </c>
+      <c r="C920" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B921" t="n">
+        <v>313.023</v>
+      </c>
+      <c r="C921" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B922" t="n">
+        <v>313.175</v>
+      </c>
+      <c r="C922" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B923" t="n">
+        <v>313.044</v>
+      </c>
+      <c r="C923" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B924" t="n">
+        <v>313.569</v>
+      </c>
+      <c r="C924" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B925" t="n">
+        <v>314.062</v>
+      </c>
+      <c r="C925" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B926" t="n">
+        <v>314.732</v>
+      </c>
+      <c r="C926" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="1" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B927" t="n">
+        <v>315.631</v>
+      </c>
+      <c r="C927" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B928" t="n">
+        <v>316.528</v>
+      </c>
+      <c r="C928" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B929" t="n">
+        <v>317.604</v>
+      </c>
+      <c r="C929" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B930" t="n">
+        <v>318.961</v>
+      </c>
+      <c r="C930" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B931" t="n">
+        <v>319.679</v>
+      </c>
+      <c r="C931" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B932" t="n">
+        <v>319.785</v>
+      </c>
+      <c r="C932" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B933" t="n">
+        <v>320.302</v>
+      </c>
+      <c r="C933" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B934" t="n">
+        <v>320.62</v>
+      </c>
+      <c r="C934" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B935" t="n">
+        <v>321.435</v>
+      </c>
+      <c r="C935" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B936" t="n">
+        <v>322.169</v>
+      </c>
+      <c r="C936" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B937" t="n">
+        <v>323.291</v>
+      </c>
+      <c r="C937" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B938" t="n">
+        <v>324.245</v>
+      </c>
+      <c r="C938" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="1" t="n">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B940" t="n">
+        <v>325.063</v>
+      </c>
+      <c r="C940" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="B65" t="n">
-        <v>338.094</v>
-      </c>
-      <c r="C65" t="n">
-        <v>3.7</v>
+      <c r="B941" t="n">
+        <v>326.031</v>
+      </c>
+      <c r="C941" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B942" t="n">
+        <v>326.588</v>
+      </c>
+      <c r="C942" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B943" t="n">
+        <v>327.46</v>
+      </c>
+      <c r="C943" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B944" t="n">
+        <v>330.293</v>
+      </c>
+      <c r="C944" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B945" t="n">
+        <v>332.407</v>
+      </c>
+      <c r="C945" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B946" t="n">
+        <v>333.979</v>
+      </c>
+      <c r="C946" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C947" t="n">
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>
